--- a/docs/analysis/extension-usecases/EU_강의실예약.xlsx
+++ b/docs/analysis/extension-usecases/EU_강의실예약.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wonsik/Documents/3_1_season/소프트웨어공학/sw-project/ExtendUsecase/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KANG\Desktop\sw-project-v1\ExtendUsecase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBCB9F9-C8AB-1C47-83D4-6B9BB58F827F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED9D66A-2CBF-4CED-B435-C18564C6E13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="21040" windowHeight="20060" xr2:uid="{92AE4BC7-A203-4649-BFE0-B881BDCEFD06}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="17400" windowHeight="14895" xr2:uid="{92AE4BC7-A203-4649-BFE0-B881BDCEFD06}"/>
   </bookViews>
   <sheets>
     <sheet name="양식" sheetId="1" r:id="rId1"/>
@@ -87,10 +87,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>학생 강의실 예약 신청</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>김시현(20223060)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -103,10 +99,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>학생이 원하는 강의실과 시간대를 선택하여 예약을 신청한다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>학생은 강의실 목록에서 원하는 강의실을 선택한 후 시간표에서 예약할 시간을 지정하고 예약 정보를 입력하여 예약을 신청한다. 학생 예약은 대기 상대로 등록된다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -187,10 +179,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>교수 강의실 예약 신청</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SFR-301, SFR-302, SFR-303, SFR-304, SFR-305, SFR-306, SFR-307, SFR-313</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -248,6 +236,18 @@
   </si>
   <si>
     <t>시스템은 예약을 승인으로 업데이트한다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>예약 등록 (교수)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>예약 등록 (학생)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>학생이 원하는 강의실과 시간대를 선택하여 예약을 사전 신청한다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -255,7 +255,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -404,7 +404,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -420,14 +420,38 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -438,53 +462,20 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -821,90 +812,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C999637-45C8-FE43-8292-D74ACEF681F0}">
   <dimension ref="B2:E55"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.42578125" customWidth="1"/>
-    <col min="4" max="5" width="37.140625" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.44140625" customWidth="1"/>
+    <col min="4" max="5" width="37.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="2:5">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="18"/>
-    </row>
-    <row r="4" spans="2:5">
+      <c r="C3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="12"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="18"/>
-    </row>
-    <row r="5" spans="2:5">
+      <c r="C4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="18"/>
-    </row>
-    <row r="6" spans="2:5">
+      <c r="C5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="12"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="18"/>
-    </row>
-    <row r="7" spans="2:5">
+      <c r="C6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="12"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
-    </row>
-    <row r="8" spans="2:5">
+      <c r="C7" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="12"/>
+    </row>
+    <row r="8" spans="2:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="18"/>
-    </row>
-    <row r="9" spans="2:5">
-      <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="13"/>
-    </row>
-    <row r="10" spans="2:5" ht="18" customHeight="1">
-      <c r="B10" s="8" t="s">
+      <c r="C8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="12"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="13"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="15"/>
+    </row>
+    <row r="10" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="16" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -917,283 +908,283 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="2:5" ht="57">
-      <c r="B11" s="9"/>
-      <c r="C11" s="25">
+    <row r="11" spans="2:5" ht="51.75" x14ac:dyDescent="0.3">
+      <c r="B11" s="17"/>
+      <c r="C11" s="9">
         <v>1</v>
       </c>
-      <c r="D11" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="26"/>
-    </row>
-    <row r="12" spans="2:5" ht="19">
-      <c r="B12" s="9"/>
-      <c r="C12" s="25">
+      <c r="D11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="17"/>
+      <c r="C12" s="9">
         <v>2</v>
       </c>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" ht="19">
-      <c r="B13" s="9"/>
-      <c r="C13" s="25">
+      <c r="D12" s="8"/>
+      <c r="E12" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="17"/>
+      <c r="C13" s="9">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="2:5" ht="38">
-      <c r="B14" s="9"/>
-      <c r="C14" s="25">
+    <row r="14" spans="2:5" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="17"/>
+      <c r="C14" s="9">
         <v>4</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" ht="19">
-      <c r="B15" s="9"/>
-      <c r="C15" s="25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="17"/>
+      <c r="C15" s="9">
         <v>5</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="2:5" ht="19">
-      <c r="B16" s="9"/>
-      <c r="C16" s="25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="17"/>
+      <c r="C16" s="9">
         <v>6</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="19">
-      <c r="B17" s="9"/>
-      <c r="C17" s="25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="17"/>
+      <c r="C17" s="9">
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="2:5" ht="38">
-      <c r="B18" s="9"/>
-      <c r="C18" s="25">
+    <row r="18" spans="2:5" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B18" s="17"/>
+      <c r="C18" s="9">
         <v>8</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="38">
-      <c r="B19" s="9"/>
-      <c r="C19" s="25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B19" s="17"/>
+      <c r="C19" s="9">
         <v>9</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="18"/>
+      <c r="C20" s="9">
+        <v>10</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" ht="19">
-      <c r="B20" s="10"/>
-      <c r="C20" s="25">
-        <v>10</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="2:5">
-      <c r="B21" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="18"/>
-    </row>
-    <row r="22" spans="2:5">
-      <c r="B22" s="19"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="12"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="22"/>
       <c r="C22" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D22" s="20" t="s">
-        <v>26</v>
+      <c r="D22" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="2:5" ht="19">
-      <c r="B23" s="19"/>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" s="22"/>
       <c r="C23" s="2">
         <v>1.2</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" ht="38">
-      <c r="B24" s="19"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B24" s="22"/>
       <c r="C24" s="2">
         <v>1.3</v>
       </c>
-      <c r="D24" s="20"/>
+      <c r="D24" s="5"/>
       <c r="E24" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" ht="38">
-      <c r="B25" s="19"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B25" s="22"/>
       <c r="C25" s="2">
         <v>2.1</v>
       </c>
-      <c r="D25" s="21" t="s">
-        <v>29</v>
+      <c r="D25" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" ht="19">
-      <c r="B26" s="19"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26" s="22"/>
       <c r="C26" s="2">
         <v>2.2000000000000002</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" ht="38">
-      <c r="B27" s="19"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B27" s="22"/>
       <c r="C27" s="2">
         <v>2.2999999999999998</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" ht="38">
-      <c r="B28" s="19"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B28" s="22"/>
       <c r="C28" s="2">
         <v>3.1</v>
       </c>
-      <c r="D28" s="21" t="s">
-        <v>33</v>
+      <c r="D28" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="2:5" ht="38">
-      <c r="B29" s="19"/>
+    <row r="29" spans="2:5" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B29" s="22"/>
       <c r="C29" s="2">
         <v>3.2</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" ht="38">
-      <c r="B30" s="22"/>
-      <c r="C30" s="20">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B30" s="23"/>
+      <c r="C30" s="5">
         <v>3.3</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-    </row>
-    <row r="33" spans="2:5">
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="7"/>
-    </row>
-    <row r="34" spans="2:5">
+      <c r="C33" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="11"/>
+      <c r="E33" s="12"/>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="7"/>
-    </row>
-    <row r="35" spans="2:5">
+      <c r="C34" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="11"/>
+      <c r="E34" s="12"/>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="7"/>
-    </row>
-    <row r="36" spans="2:5">
+      <c r="C35" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="11"/>
+      <c r="E35" s="12"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="6"/>
-      <c r="E36" s="7"/>
-    </row>
-    <row r="37" spans="2:5">
+      <c r="C36" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="11"/>
+      <c r="E36" s="12"/>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="7"/>
-    </row>
-    <row r="38" spans="2:5">
+      <c r="C37" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="11"/>
+      <c r="E37" s="12"/>
+    </row>
+    <row r="38" spans="2:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D38" s="6"/>
-      <c r="E38" s="7"/>
-    </row>
-    <row r="39" spans="2:5">
-      <c r="B39" s="11"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="13"/>
-    </row>
-    <row r="40" spans="2:5">
-      <c r="B40" s="8" t="s">
+      <c r="C38" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="11"/>
+      <c r="E38" s="12"/>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B39" s="13"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="15"/>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B40" s="16" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="3" t="s">
@@ -1206,178 +1197,178 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="2:5" ht="38">
-      <c r="B41" s="9"/>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B41" s="17"/>
       <c r="C41" s="2">
         <v>1</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="2:5" ht="38">
-      <c r="B42" s="9"/>
+    <row r="42" spans="2:5" ht="34.5" x14ac:dyDescent="0.3">
+      <c r="B42" s="17"/>
       <c r="C42" s="2">
         <v>2</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" ht="38">
-      <c r="B43" s="9"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B43" s="17"/>
       <c r="C43" s="2">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E43" s="1"/>
     </row>
-    <row r="44" spans="2:5" ht="38">
-      <c r="B44" s="9"/>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B44" s="17"/>
       <c r="C44" s="2">
         <v>4</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" ht="19">
-      <c r="B45" s="9"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B45" s="17"/>
       <c r="C45" s="2">
         <v>5</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E45" s="1"/>
     </row>
-    <row r="46" spans="2:5" ht="19">
-      <c r="B46" s="9"/>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B46" s="17"/>
       <c r="C46" s="2">
         <v>6</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5">
-      <c r="B47" s="10"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B47" s="18"/>
       <c r="C47" s="2">
         <v>7</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
     </row>
-    <row r="48" spans="2:5">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D48" s="17"/>
-      <c r="E48" s="18"/>
-    </row>
-    <row r="49" spans="2:5" ht="57">
+      <c r="C48" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D48" s="11"/>
+      <c r="E48" s="12"/>
+    </row>
+    <row r="49" spans="2:5" ht="34.5" x14ac:dyDescent="0.3">
       <c r="B49" s="4"/>
       <c r="C49" s="2">
         <v>1</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E49" s="1"/>
     </row>
-    <row r="50" spans="2:5" ht="57">
+    <row r="50" spans="2:5" ht="51.75" x14ac:dyDescent="0.3">
       <c r="B50" s="4"/>
       <c r="C50" s="2">
         <v>2</v>
       </c>
-      <c r="D50" s="23"/>
+      <c r="D50" s="7"/>
       <c r="E50" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" ht="38">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" ht="34.5" x14ac:dyDescent="0.3">
       <c r="B51" s="4"/>
       <c r="C51" s="2">
         <v>3</v>
       </c>
-      <c r="D51" s="23"/>
+      <c r="D51" s="7"/>
       <c r="E51" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D52" s="17"/>
-      <c r="E52" s="18"/>
-    </row>
-    <row r="53" spans="2:5" ht="38">
+      <c r="C52" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D52" s="11"/>
+      <c r="E52" s="12"/>
+    </row>
+    <row r="53" spans="2:5" ht="34.5" x14ac:dyDescent="0.3">
       <c r="B53" s="4"/>
       <c r="C53" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D53" s="21" t="s">
-        <v>33</v>
+      <c r="D53" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="E53" s="1"/>
     </row>
-    <row r="54" spans="2:5" ht="38">
+    <row r="54" spans="2:5" ht="34.5" x14ac:dyDescent="0.3">
       <c r="B54" s="4"/>
       <c r="C54" s="2">
         <v>1.2</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5" ht="57">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" ht="34.5" x14ac:dyDescent="0.3">
       <c r="B55" s="4"/>
-      <c r="C55" s="20">
+      <c r="C55" s="5">
         <v>1.3</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:B20"/>
+    <mergeCell ref="B21:B30"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:E36"/>
     <mergeCell ref="C52:E52"/>
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="C38:E38"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B40:B47"/>
     <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:B20"/>
-    <mergeCell ref="B21:B30"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
